--- a/results/Int Task Remove ACC 0.3/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.3/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.01698497117501184</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02618648756139345</v>
+        <v>0.02618627139336722</v>
       </c>
       <c r="F3" t="n">
         <v>-0.0009056446009383069</v>
@@ -1166,13 +1166,13 @@
         <v>0.04507651983262906</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001762286377002202</v>
+        <v>0.001754279971878103</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0001188804049217418</v>
+        <v>-0.0001148772023596922</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03229055872694077</v>
+        <v>0.03228633923997543</v>
       </c>
       <c r="K3" t="n">
         <v>0.01729894161556222</v>
@@ -1187,7 +1187,7 @@
         <v>0.0458959011269988</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01326323622852804</v>
+        <v>0.01326739769336366</v>
       </c>
       <c r="P3" t="n">
         <v>0.01997892560516707</v>
@@ -1196,7 +1196,7 @@
         <v>0.01254223890544111</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01389997544489576</v>
+        <v>0.01390411164969515</v>
       </c>
       <c r="S3" t="n">
         <v>0.3158853213324768</v>
@@ -1208,7 +1208,7 @@
         <v>0.1821920335084221</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0001310796821632409</v>
+        <v>-0.0001268868100458409</v>
       </c>
       <c r="W3" t="n">
         <v>0.01204618343985155</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1064630293149331</v>
+        <v>0.1064588258681067</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.09615205162205211</v>
+        <v>0.09615225186631646</v>
       </c>
       <c r="AL3" t="n">
         <v>6.775563989417475e-05</v>
@@ -1301,7 +1301,7 @@
         <v>0.02506754458932125</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.009673504267477049</v>
+        <v>0.009669501064914999</v>
       </c>
       <c r="BB3" t="n">
         <v>0.001460895026783691</v>
@@ -1394,7 +1394,7 @@
         <v>0.002316247295115551</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.001555632793322972</v>
+        <v>-0.001551436402219322</v>
       </c>
       <c r="CG3" t="n">
         <v>0.02074341264668677</v>
@@ -1428,7 +1428,7 @@
         <v>0.0506044210323213</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03621319221631743</v>
+        <v>0.03620614670616922</v>
       </c>
       <c r="F4" t="n">
         <v>0.004465645007068365</v>
@@ -1437,13 +1437,13 @@
         <v>0.06301557666658215</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007407235175377051</v>
+        <v>0.007409202358340407</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009868339661043724</v>
+        <v>0.0009867292400717008</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04238072220076395</v>
+        <v>0.04237898617671944</v>
       </c>
       <c r="K4" t="n">
         <v>0.01337581736023407</v>
@@ -1458,7 +1458,7 @@
         <v>0.05009213909791246</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02459180398835202</v>
+        <v>0.02459825632051754</v>
       </c>
       <c r="P4" t="n">
         <v>0.0230164888205325</v>
@@ -1467,7 +1467,7 @@
         <v>0.0212564095150025</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02204093980603921</v>
+        <v>0.02204129425766014</v>
       </c>
       <c r="S4" t="n">
         <v>0.1574953257748061</v>
@@ -1479,7 +1479,7 @@
         <v>0.1046274088201366</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0009891951741788309</v>
+        <v>0.0009875303445424208</v>
       </c>
       <c r="W4" t="n">
         <v>0.01980281247188319</v>
@@ -1521,10 +1521,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.05636049418228607</v>
+        <v>0.05635384135739291</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.06248940730209827</v>
+        <v>0.0624974167805883</v>
       </c>
       <c r="AL4" t="n">
         <v>0.001115949583367558</v>
@@ -1572,7 +1572,7 @@
         <v>0.04083352883010267</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0120729713123251</v>
+        <v>0.01207636446170939</v>
       </c>
       <c r="BB4" t="n">
         <v>0.005890265933019624</v>
@@ -1665,7 +1665,7 @@
         <v>0.004154362292816068</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.02633817164850317</v>
+        <v>0.02632978696832615</v>
       </c>
       <c r="CG4" t="n">
         <v>0.04488275019360632</v>
@@ -1936,7 +1936,7 @@
         <v>-0.004539722572509441</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.048929920268569</v>
+        <v>-0.04888795635753249</v>
       </c>
       <c r="CG5" t="n">
         <v>-0.01019558884727421</v>
@@ -1970,7 +1970,7 @@
         <v>0.0008936124859280415</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.002539867904467291</v>
+        <v>-0.002529859898062167</v>
       </c>
       <c r="F6" t="n">
         <v>-0.00194670221929851</v>
@@ -1985,7 +1985,7 @@
         <v>-0.0004291412463979821</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001178271442174878</v>
+        <v>-0.001209970512335481</v>
       </c>
       <c r="K6" t="n">
         <v>0.006472623292563259</v>
@@ -2009,7 +2009,7 @@
         <v>0.005183368146091008</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.004040941967437039</v>
+        <v>-0.004030933961031915</v>
       </c>
       <c r="S6" t="n">
         <v>0.1950561547935448</v>
@@ -2021,7 +2021,7 @@
         <v>0.1186484661468762</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0004605877872784825</v>
+        <v>-0.0004291412463979821</v>
       </c>
       <c r="W6" t="n">
         <v>0.001900385238972882</v>
@@ -2066,7 +2066,7 @@
         <v>0.06342224049771486</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.05987988892987048</v>
+        <v>0.05984986491065511</v>
       </c>
       <c r="AL6" t="n">
         <v>-0.0006203495382233499</v>
@@ -2114,7 +2114,7 @@
         <v>-0.0003032872629653988</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.001712489488446101</v>
+        <v>0.001682465469230729</v>
       </c>
       <c r="BB6" t="n">
         <v>-0.0007436070759871515</v>
@@ -2241,7 +2241,7 @@
         <v>0.02613401663084107</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03431220770843412</v>
+        <v>0.03433317206902113</v>
       </c>
       <c r="F7" t="n">
         <v>-0.0003358527577519088</v>
@@ -2250,10 +2250,10 @@
         <v>0.04307921885569166</v>
       </c>
       <c r="H7" t="n">
-        <v>8.006405124100224e-05</v>
+        <v>4.003202562050667e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.074041773725056e-05</v>
+        <v>-2.072440492700278e-05</v>
       </c>
       <c r="J7" t="n">
         <v>0.02466553739715897</v>
@@ -2280,7 +2280,7 @@
         <v>0.01588532582929967</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0121095938960006</v>
+        <v>0.01208927695166903</v>
       </c>
       <c r="S7" t="n">
         <v>0.318598542119884</v>
@@ -2512,7 +2512,7 @@
         <v>0.05287486513585227</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05810697825165471</v>
+        <v>0.05806486838688041</v>
       </c>
       <c r="F8" t="n">
         <v>0.001161720054362236</v>
@@ -2527,7 +2527,7 @@
         <v>0.0004725462729272129</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05881455910181397</v>
+        <v>0.05880406812405484</v>
       </c>
       <c r="K8" t="n">
         <v>0.02409039630301516</v>
